--- a/data/trans_dic/IP31KM01_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,69; 94,62</t>
+          <t>85,58; 94,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,72; 94,02</t>
+          <t>83,67; 94,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,38; 92,63</t>
+          <t>86,88; 93,72</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,47; 95,79</t>
+          <t>80,45; 93,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,37; 92,92</t>
+          <t>87,37; 96,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,36; 93,34</t>
+          <t>86,14; 93,79</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,34; 99,17</t>
+          <t>74,63; 91,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,59; 92,17</t>
+          <t>88,96; 99,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 94,33</t>
+          <t>84,73; 94,58</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,04; 94,22</t>
+          <t>88,75; 96,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,43; 95,9</t>
+          <t>84,08; 92,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,13; 94,49</t>
+          <t>88,05; 93,43</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,83; 92,89</t>
+          <t>81,77; 93,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,27; 93,32</t>
+          <t>82,4; 92,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,07; 92,45</t>
+          <t>83,93; 92,14</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,65; 96,27</t>
+          <t>80,16; 94,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,08; 94,08</t>
+          <t>86,37; 96,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,39; 93,89</t>
+          <t>85,14; 94,33</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,98; 92,91</t>
+          <t>87,66; 92,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,76; 91,8</t>
+          <t>88,24; 92,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,67; 91,71</t>
+          <t>88,61; 91,62</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91916</t>
+          <t>110313</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>118652</t>
+          <t>90260</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210569</t>
+          <t>200573</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86139; 96238</t>
+          <t>103733; 114824</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99654; 127091</t>
+          <t>83966; 94580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192788; 219422</t>
+          <t>192479; 207639</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>88316</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168333</t>
+          <t>167069</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80753; 89463</t>
+          <t>72309; 83610</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74378; 87071</t>
+          <t>83357; 91737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159707; 174632</t>
+          <t>159600; 173790</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>47869</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53580</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101718</t>
+          <t>97883</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44749; 49675</t>
+          <t>41675; 50872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47742; 57452</t>
+          <t>46269; 51634</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95678; 106048</t>
+          <t>91389; 102006</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>242</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>195302</t>
+          <t>183543</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>198731</t>
+          <t>157034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>394034</t>
+          <t>340577</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>185446; 203071</t>
+          <t>175110; 189487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>190174; 203947</t>
+          <t>148522; 163374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>381639; 404582</t>
+          <t>329252; 349390</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>152</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>102719</t>
+          <t>129384</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>142883</t>
+          <t>102197</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245603</t>
+          <t>231581</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95677; 107298</t>
+          <t>119040; 136010</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>131181; 148803</t>
+          <t>95143; 107308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233921; 254215</t>
+          <t>219089; 240530</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>58197</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>64974</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>123172</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58321; 66325</t>
+          <t>52799; 62048</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54589; 64944</t>
+          <t>60764; 68032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116388; 129499</t>
+          <t>115983; 128500</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>818</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>587846</t>
+          <t>608060</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>656649</t>
+          <t>552796</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1244495</t>
+          <t>1160856</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>574044; 599398</t>
+          <t>592319; 621833</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>635429; 672294</t>
+          <t>538478; 563499</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1221402; 1263304</t>
+          <t>1139476; 1178173</t>
         </is>
       </c>
     </row>
